--- a/VFL_2026_Santiago_Pricing.xlsx
+++ b/VFL_2026_Santiago_Pricing.xlsx
@@ -2668,70 +2668,70 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>happywei</t>
+          <t>kamo</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Xi Lai Gaming</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>Minny</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>EDward Gaming</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>22.3</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Minny</t>
+          <t>BABYBAY</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2740,52 +2740,52 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>22.3</v>
+        <v>20.6</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>NoMan</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Xi Lai Gaming</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>17.7</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GLYPH</t>
+          <t>wayne</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2794,40 +2794,40 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>17.7</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BABYBAY</t>
+          <t>NoMan</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>G2 Esports</t>
+          <t>Xi Lai Gaming</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>20.6</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -2838,13 +2838,13 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>49.5</v>
+        <v>50</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>179.6</v>
+        <v>127.2</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11">
@@ -2906,12 +2906,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>kamo</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>EDward Gaming</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
     </row>
@@ -2960,81 +2960,81 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GLYPH</t>
+          <t>BABYBAY</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>BABYBAY</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>G2 Esports</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Xross</t>
+          <t>koalanoob</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Nongshim RedForce</t>
+          <t>FURIA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
     </row>
@@ -3076,17 +3076,17 @@
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>154.1</v>
+        <v>159.8</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>happywei -&gt; Xross | NoMan -&gt; Lovers rock</t>
+          <t>wayne -&gt; koalanoob | NoMan -&gt; Lovers rock</t>
         </is>
       </c>
     </row>
@@ -3149,27 +3149,27 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>BABYBAY</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>EDward Gaming</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
     </row>
@@ -3203,12 +3203,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>BABYBAY</t>
+          <t>koalanoob</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>G2 Esports</t>
+          <t>FURIA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3217,52 +3217,52 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Xross</t>
+          <t>Lovers rock</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Nongshim RedForce</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>skuba</t>
+          <t>Ivy</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>Nongshim RedForce</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3271,46 +3271,46 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>21.2</v>
+        <v>20.4</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>invy</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Nongshim RedForce</t>
+          <t>Paper Rex</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>16.7</v>
+        <v>23.7</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
@@ -3319,17 +3319,17 @@
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>90</v>
+        <v>80.7</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Minny -&gt; skuba | Lovers rock -&gt; Francis</t>
+          <t>Minny -&gt; Ivy | kamo -&gt; invy</t>
         </is>
       </c>
     </row>

--- a/VFL_2026_Santiago_Pricing.xlsx
+++ b/VFL_2026_Santiago_Pricing.xlsx
@@ -2668,7 +2668,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>kamo</t>
+          <t>wayne</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -2688,40 +2688,36 @@
         <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Minny</t>
+          <t>kamo</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>22.3</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2743,91 +2739,95 @@
         <v>9</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>20.6</v>
+        <v>28.7</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GLYPH</t>
+          <t>NoMan</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Xi Lai Gaming</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>17.7</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>wayne</t>
+          <t>Stax</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>NoMan</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Xi Lai Gaming</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>15.1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -2841,10 +2841,10 @@
         <v>50</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>127.2</v>
+        <v>145.9</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11">
@@ -2926,19 +2926,19 @@
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Minny</t>
+          <t>BABYBAY</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2947,40 +2947,40 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>BABYBAY</t>
+          <t>Stax</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>G2 Esports</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
     </row>
@@ -3007,34 +3007,34 @@
         <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>koalanoob</t>
+          <t>Xross</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FURIA</t>
+          <t>Nongshim RedForce</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
     </row>
@@ -3076,17 +3076,17 @@
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>159.8</v>
+        <v>157.9</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>wayne -&gt; koalanoob | NoMan -&gt; Lovers rock</t>
+          <t>wayne -&gt; Xross | NoMan -&gt; Lovers rock</t>
         </is>
       </c>
     </row>
@@ -3149,115 +3149,115 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>BABYBAY</t>
+          <t>kamo</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>G2 Esports</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GLYPH</t>
+          <t>BABYBAY</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>koalanoob</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>FURIA</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Lovers rock</t>
+          <t>Xross</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>Nongshim RedForce</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Ivy</t>
+          <t>Francis</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -3267,44 +3267,44 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>20.4</v>
+        <v>21.3</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>invy</t>
+          <t>skuba</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Paper Rex</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>23.7</v>
+        <v>28.5</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -3322,14 +3322,14 @@
         <v>50</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>80.7</v>
+        <v>119.5</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>177</v>
+        <v>105</v>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Minny -&gt; Ivy | kamo -&gt; invy</t>
+          <t>Lovers rock -&gt; Francis | Stax -&gt; skuba</t>
         </is>
       </c>
     </row>

--- a/VFL_2026_Santiago_Pricing.xlsx
+++ b/VFL_2026_Santiago_Pricing.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -506,8 +506,10 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -543,15 +545,25 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Actual Best-2 Pts</t>
+          <t>Best-2 GW1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Best-2 GW2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Best-2 GW3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Pick%</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Uncertainty</t>
         </is>
@@ -583,12 +595,18 @@
         <v>5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H2" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>39.7</v>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -616,12 +634,18 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H3" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -649,12 +673,18 @@
         <v>-1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J4" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -682,12 +712,18 @@
         <v>-1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H5" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J5" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -715,12 +751,18 @@
         <v>-1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H6" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J6" s="2" t="n">
         <v>13.2</v>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -751,9 +793,15 @@
         <v>26</v>
       </c>
       <c r="H7" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="2" t="n">
         <v>24.4</v>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -781,12 +829,18 @@
         <v>-3</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H8" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J8" s="2" t="n">
         <v>25.6</v>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -814,12 +868,18 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H9" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="2" t="n">
         <v>33.2</v>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -850,9 +910,15 @@
         <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J10" s="2" t="n">
         <v>28.7</v>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -883,9 +949,15 @@
         <v>12</v>
       </c>
       <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="n">
         <v>27.1</v>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -913,12 +985,18 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H12" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J12" s="2" t="n">
         <v>41.9</v>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -946,12 +1024,18 @@
         <v>-4.5</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="H13" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J13" s="2" t="n">
         <v>50.1</v>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -979,12 +1063,18 @@
         <v>-1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="H14" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J14" s="2" t="n">
         <v>45.8</v>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1015,9 +1105,15 @@
         <v>17</v>
       </c>
       <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1045,12 +1141,18 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H16" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1081,9 +1183,15 @@
         <v>14</v>
       </c>
       <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2" t="n">
         <v>11.3</v>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1114,9 +1222,15 @@
         <v>20</v>
       </c>
       <c r="H18" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J18" s="2" t="n">
         <v>29.5</v>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1144,12 +1258,18 @@
         <v>-1.5</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J19" s="2" t="n">
         <v>6.7</v>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1177,12 +1297,18 @@
         <v>1.5</v>
       </c>
       <c r="G20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I20" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="J20" s="2" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1213,9 +1339,15 @@
         <v>13</v>
       </c>
       <c r="H21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2" t="n">
         <v>5.9</v>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1246,9 +1378,15 @@
         <v>22</v>
       </c>
       <c r="H22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1279,9 +1417,15 @@
         <v>14</v>
       </c>
       <c r="H23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2" t="n">
         <v>42.7</v>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1312,9 +1456,15 @@
         <v>19</v>
       </c>
       <c r="H24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2" t="n">
         <v>10.4</v>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1345,9 +1495,15 @@
         <v>5</v>
       </c>
       <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2" t="n">
         <v>7.8</v>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1378,9 +1534,15 @@
         <v>13</v>
       </c>
       <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="n">
         <v>10.2</v>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1411,9 +1573,15 @@
         <v>9</v>
       </c>
       <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="n">
         <v>5.5</v>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1441,12 +1609,18 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="J28" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1474,12 +1648,18 @@
         <v>0.5</v>
       </c>
       <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I29" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="J29" s="2" t="n">
         <v>25.9</v>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>HIGH UNCERTAINTY - MANUAL REVIEW NEEDED</t>
         </is>
@@ -1514,9 +1694,15 @@
         <v>2</v>
       </c>
       <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="n">
         <v>12.8</v>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1544,12 +1730,18 @@
         <v>-1.5</v>
       </c>
       <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="H31" s="2" t="n">
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="n">
         <v>8.4</v>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>HIGH UNCERTAINTY - MANUAL REVIEW NEEDED</t>
         </is>
@@ -1584,9 +1776,15 @@
         <v>3</v>
       </c>
       <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="n">
         <v>25.6</v>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1617,9 +1815,15 @@
         <v>14</v>
       </c>
       <c r="H33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2" t="n">
         <v>22.1</v>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1650,9 +1854,15 @@
         <v>18</v>
       </c>
       <c r="H34" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1680,12 +1890,18 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I35" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="J35" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1713,12 +1929,18 @@
         <v>-0.5</v>
       </c>
       <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2" t="n">
         <v>1.4</v>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>HIGH UNCERTAINTY - MANUAL REVIEW NEEDED</t>
         </is>
@@ -1750,12 +1972,18 @@
         <v>-2</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H37" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J37" s="2" t="n">
         <v>28.4</v>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1783,12 +2011,18 @@
         <v>-1</v>
       </c>
       <c r="G38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="2" t="n">
         <v>11.6</v>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>HIGH UNCERTAINTY - MANUAL REVIEW NEEDED</t>
         </is>
@@ -1820,12 +2054,18 @@
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="2" t="n">
         <v>2.9</v>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>HIGH UNCERTAINTY - MANUAL REVIEW NEEDED</t>
         </is>
@@ -1860,9 +2100,15 @@
         <v>5</v>
       </c>
       <c r="H40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1893,9 +2139,15 @@
         <v>17</v>
       </c>
       <c r="H41" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1926,9 +2178,15 @@
         <v>3</v>
       </c>
       <c r="H42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1959,9 +2217,15 @@
         <v>-2</v>
       </c>
       <c r="H43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="2" t="n">
         <v>13.4</v>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>HIGH UNCERTAINTY - MANUAL REVIEW NEEDED</t>
         </is>
@@ -1993,12 +2257,18 @@
         <v>-4</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H44" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J44" s="2" t="n">
         <v>23.1</v>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2026,12 +2296,18 @@
         <v>-3.5</v>
       </c>
       <c r="G45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="I45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2062,9 +2338,15 @@
         <v>15</v>
       </c>
       <c r="H46" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="n">
         <v>11.6</v>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2092,12 +2374,18 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H47" s="2" t="n">
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2125,12 +2413,18 @@
         <v>-0.5</v>
       </c>
       <c r="G48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="H48" s="2" t="n">
+      <c r="I48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2158,12 +2452,18 @@
         <v>-1</v>
       </c>
       <c r="G49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H49" s="2" t="n">
+      <c r="I49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="2" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>HIGH UNCERTAINTY - MANUAL REVIEW NEEDED</t>
         </is>
@@ -2195,12 +2495,18 @@
         <v>1</v>
       </c>
       <c r="G50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="H50" s="2" t="n">
+      <c r="I50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>HIGH UNCERTAINTY - MANUAL REVIEW NEEDED</t>
         </is>
@@ -2232,12 +2538,18 @@
         <v>-2.5</v>
       </c>
       <c r="G51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H51" s="2" t="n">
+      <c r="I51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="2" t="n">
         <v>5.8</v>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2268,9 +2580,15 @@
         <v>2</v>
       </c>
       <c r="H52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="2" t="n">
         <v>13.1</v>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2298,12 +2616,18 @@
         <v>-2</v>
       </c>
       <c r="G53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="H53" s="2" t="n">
+      <c r="I53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="2" t="n">
         <v>5.1</v>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>HIGH UNCERTAINTY - MANUAL REVIEW NEEDED</t>
         </is>
@@ -2338,9 +2662,15 @@
         <v>1</v>
       </c>
       <c r="H54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="2" t="n">
         <v>2.8</v>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2368,12 +2698,18 @@
         <v>0.5</v>
       </c>
       <c r="G55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="H55" s="2" t="n">
+      <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>HIGH UNCERTAINTY - MANUAL REVIEW NEEDED</t>
         </is>
@@ -2408,9 +2744,15 @@
         <v>17</v>
       </c>
       <c r="H56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="2" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2441,9 +2783,15 @@
         <v>24</v>
       </c>
       <c r="H57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2471,12 +2819,18 @@
         <v>-4.5</v>
       </c>
       <c r="G58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H58" s="2" t="n">
+      <c r="I58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="2" t="n">
         <v>5.8</v>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>HIGH UNCERTAINTY - MANUAL REVIEW NEEDED</t>
         </is>
@@ -2508,12 +2862,18 @@
         <v>-1</v>
       </c>
       <c r="G59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H59" s="2" t="n">
+      <c r="I59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2541,12 +2901,18 @@
         <v>-0.5</v>
       </c>
       <c r="G60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>HIGH UNCERTAINTY - MANUAL REVIEW NEEDED</t>
         </is>
@@ -2581,9 +2947,15 @@
         <v>4</v>
       </c>
       <c r="H61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2668,24 +3040,24 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>wayne</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>22.6</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>14</v>
@@ -2695,60 +3067,60 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>kamo</t>
+          <t>BABYBAY</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>28.7</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BABYBAY</t>
+          <t>wayne</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>G2 Esports</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>28.7</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2780,34 +3152,34 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Stax</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GLYPH</t>
+          <t>starxo</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -2817,17 +3189,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>15.1</v>
+        <v>14.4</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -2838,13 +3210,13 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>50</v>
+        <v>49.5</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>145.9</v>
+        <v>338.1</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
@@ -2906,12 +3278,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>kamo</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2920,13 +3292,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
     </row>
@@ -2960,34 +3332,34 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Stax</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GLYPH</t>
+          <t>starxo</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -2997,7 +3369,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -3007,7 +3379,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -3076,13 +3448,13 @@
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>50</v>
+        <v>49.5</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>157.9</v>
+        <v>194.9</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
@@ -3149,12 +3521,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>kamo</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3163,13 +3535,13 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
     </row>
@@ -3257,12 +3629,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>Lovers rock</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Nongshim RedForce</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3271,25 +3643,25 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>21.3</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>skuba</t>
+          <t>Ivy</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>Nongshim RedForce</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3298,13 +3670,13 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>28.5</v>
+        <v>26.4</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -3319,17 +3691,17 @@
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>50</v>
+        <v>49.5</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>119.5</v>
+        <v>117.3</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Lovers rock -&gt; Francis | Stax -&gt; skuba</t>
+          <t>starxo -&gt; Ivy</t>
         </is>
       </c>
     </row>

--- a/VFL_2026_Santiago_Pricing.xlsx
+++ b/VFL_2026_Santiago_Pricing.xlsx
@@ -2968,17 +2968,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2994,6 +2995,7 @@
       <c r="F1" s="6" t="n"/>
       <c r="G1" s="6" t="n"/>
       <c r="H1" s="6" t="n"/>
+      <c r="I1" s="6" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -3008,30 +3010,35 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
+          <t>Slot</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>VP</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Expected Best-2</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Actual Best-2</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>IGL</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Transfers</t>
         </is>
@@ -3040,60 +3047,70 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>BABYBAY</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>9.5</v>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>22.6</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+        <v>28.7</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BABYBAY</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>G2 Esports</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>9</v>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>28.7</v>
+        <v>9.5</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
+        <v>22.6</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3111,16 +3128,21 @@
           <t>C</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3138,21 +3160,26 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GLYPH</t>
+          <t>starxo</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3162,24 +3189,29 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>15.2</v>
-      </c>
       <c r="F7" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
+        <v>14.5</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>starxo</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3189,19 +3221,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>14.4</v>
-      </c>
       <c r="F8" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+        <v>15.1</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -3209,13 +3246,13 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="E9" s="9" t="n">
         <v>49.5</v>
       </c>
-      <c r="E9" s="9" t="n">
-        <v>338.1</v>
-      </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="9" t="n">
+        <v>336.3</v>
+      </c>
+      <c r="G9" s="10" t="n">
         <v>102</v>
       </c>
     </row>
@@ -3232,6 +3269,7 @@
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
       <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -3246,30 +3284,35 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
+          <t>Slot</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>VP</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Expected Best-2</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>Actual Best-2</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>IGL</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Transfers</t>
         </is>
@@ -3278,61 +3321,71 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>BABYBAY</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>9.5</v>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>23.4</v>
+        <v>9</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BABYBAY</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>G2 Esports</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>9</v>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>18</v>
+        <v>9.5</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
+        <v>23.4</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GLYPH</t>
+          <t>starxo</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -3342,24 +3395,29 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>starxo</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -3369,19 +3427,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F16" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3399,16 +3462,21 @@
           <t>C</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
         <v>7.5</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="F17" s="2" t="n">
         <v>23.1</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="G17" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3426,16 +3494,21 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
         <v>9.5</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>IGL</t>
         </is>
@@ -3447,16 +3520,16 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="E19" s="9" t="n">
         <v>49.5</v>
       </c>
-      <c r="E19" s="9" t="n">
-        <v>194.9</v>
-      </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="9" t="n">
+        <v>195.4</v>
+      </c>
+      <c r="G19" s="10" t="n">
         <v>112</v>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>wayne -&gt; Xross | NoMan -&gt; Lovers rock</t>
         </is>
@@ -3475,6 +3548,7 @@
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -3489,30 +3563,35 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
+          <t>Slot</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>VP</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>Expected Best-2</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>Actual Best-2</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>IGL</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Transfers</t>
         </is>
@@ -3534,53 +3613,63 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
         <v>9.5</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="F23" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="G23" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>BABYBAY</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>G2 Esports</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>9</v>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GLYPH</t>
+          <t>Xross</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Nongshim RedForce</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3588,80 +3677,95 @@
           <t>C</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
-        <v>7</v>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
+        <v>23.1</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Xross</t>
+          <t>Lovers rock</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Nongshim RedForce</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>7.5</v>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>23.1</v>
+        <v>9.5</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Lovers rock</t>
+          <t>Ivy</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>Nongshim RedForce</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>9.5</v>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
+        <v>26.2</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Ivy</t>
+          <t>skuba</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Nongshim RedForce</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3669,16 +3773,21 @@
           <t>S</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
-        <v>7</v>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>26.4</v>
+        <v>9.5</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
+        <v>28.6</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>IGL</t>
         </is>
@@ -3690,18 +3799,18 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D29" s="9" t="n">
-        <v>49.5</v>
-      </c>
       <c r="E29" s="9" t="n">
-        <v>117.3</v>
-      </c>
-      <c r="F29" s="10" t="n">
-        <v>97</v>
-      </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>starxo -&gt; Ivy</t>
+        <v>50</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>130</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>110</v>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>starxo -&gt; Ivy | BABYBAY -&gt; skuba</t>
         </is>
       </c>
     </row>
